--- a/01_My_Learnings/05_NSO_work/RC1_clean.xlsx
+++ b/01_My_Learnings/05_NSO_work/RC1_clean.xlsx
@@ -673,7 +673,7 @@
         <v>1</v>
       </c>
       <c r="W2" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X2" t="n">
         <v>4</v>
@@ -780,7 +780,7 @@
         <v>1</v>
       </c>
       <c r="W3" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X3" t="n">
         <v>1</v>
@@ -887,7 +887,7 @@
         <v>1</v>
       </c>
       <c r="W4" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X4" t="n">
         <v>1</v>
@@ -994,7 +994,7 @@
         <v>1</v>
       </c>
       <c r="W5" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X5" t="n">
         <v>1</v>
@@ -1101,7 +1101,7 @@
         <v>1</v>
       </c>
       <c r="W6" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X6" t="n">
         <v>1</v>
@@ -1208,7 +1208,7 @@
         <v>1</v>
       </c>
       <c r="W7" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X7" t="n">
         <v>1</v>
@@ -1315,7 +1315,7 @@
         <v>1</v>
       </c>
       <c r="W8" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X8" t="n">
         <v>1</v>
@@ -1422,7 +1422,7 @@
         <v>1</v>
       </c>
       <c r="W9" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X9" t="n">
         <v>1</v>
@@ -1529,7 +1529,7 @@
         <v>1</v>
       </c>
       <c r="W10" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X10" t="n">
         <v>1</v>
@@ -1636,7 +1636,7 @@
         <v>1</v>
       </c>
       <c r="W11" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X11" t="n">
         <v>1</v>
@@ -1743,7 +1743,7 @@
         <v>1</v>
       </c>
       <c r="W12" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X12" t="n">
         <v>1</v>
@@ -1850,7 +1850,7 @@
         <v>1</v>
       </c>
       <c r="W13" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X13" t="n">
         <v>8</v>
@@ -1957,7 +1957,7 @@
         <v>1</v>
       </c>
       <c r="W14" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X14" t="n">
         <v>8</v>
@@ -2064,7 +2064,7 @@
         <v>1</v>
       </c>
       <c r="W15" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X15" t="n">
         <v>8</v>
@@ -2171,7 +2171,7 @@
         <v>1</v>
       </c>
       <c r="W16" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X16" t="n">
         <v>1</v>
@@ -2278,7 +2278,7 @@
         <v>1</v>
       </c>
       <c r="W17" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -2385,7 +2385,7 @@
         <v>1</v>
       </c>
       <c r="W18" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -2492,7 +2492,7 @@
         <v>1</v>
       </c>
       <c r="W19" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -2599,7 +2599,7 @@
         <v>1</v>
       </c>
       <c r="W20" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2706,7 +2706,7 @@
         <v>1</v>
       </c>
       <c r="W21" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X21" t="n">
         <v>1</v>
@@ -2813,7 +2813,7 @@
         <v>1</v>
       </c>
       <c r="W22" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X22" t="n">
         <v>1</v>
@@ -2920,7 +2920,7 @@
         <v>1</v>
       </c>
       <c r="W23" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X23" t="n">
         <v>1</v>
@@ -3027,7 +3027,7 @@
         <v>1</v>
       </c>
       <c r="W24" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X24" t="n">
         <v>1</v>
@@ -3134,7 +3134,7 @@
         <v>1</v>
       </c>
       <c r="W25" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X25" t="n">
         <v>1</v>
@@ -3241,7 +3241,7 @@
         <v>1</v>
       </c>
       <c r="W26" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X26" t="n">
         <v>4</v>
@@ -3348,7 +3348,7 @@
         <v>1</v>
       </c>
       <c r="W27" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X27" t="n">
         <v>1</v>
@@ -3455,7 +3455,7 @@
         <v>1</v>
       </c>
       <c r="W28" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X28" t="n">
         <v>1</v>
@@ -3562,7 +3562,7 @@
         <v>1</v>
       </c>
       <c r="W29" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X29" t="n">
         <v>1</v>
@@ -3669,7 +3669,7 @@
         <v>1</v>
       </c>
       <c r="W30" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X30" t="n">
         <v>1</v>
@@ -3776,7 +3776,7 @@
         <v>1</v>
       </c>
       <c r="W31" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X31" t="n">
         <v>1</v>
@@ -3883,7 +3883,7 @@
         <v>1</v>
       </c>
       <c r="W32" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X32" t="n">
         <v>1</v>
@@ -3990,7 +3990,7 @@
         <v>1</v>
       </c>
       <c r="W33" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X33" t="n">
         <v>4</v>
@@ -4097,7 +4097,7 @@
         <v>1</v>
       </c>
       <c r="W34" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X34" t="n">
         <v>1</v>
@@ -4204,7 +4204,7 @@
         <v>1</v>
       </c>
       <c r="W35" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X35" t="n">
         <v>1</v>
@@ -4311,7 +4311,7 @@
         <v>1</v>
       </c>
       <c r="W36" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X36" t="n">
         <v>1</v>
@@ -4418,7 +4418,7 @@
         <v>1</v>
       </c>
       <c r="W37" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X37" t="n">
         <v>1</v>
@@ -4525,7 +4525,7 @@
         <v>1</v>
       </c>
       <c r="W38" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X38" t="n">
         <v>1</v>
@@ -4632,7 +4632,7 @@
         <v>1</v>
       </c>
       <c r="W39" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X39" t="n">
         <v>1</v>
@@ -4739,7 +4739,7 @@
         <v>1</v>
       </c>
       <c r="W40" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X40" t="n">
         <v>1</v>
@@ -4846,7 +4846,7 @@
         <v>1</v>
       </c>
       <c r="W41" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X41" t="n">
         <v>1</v>
@@ -4953,7 +4953,7 @@
         <v>1</v>
       </c>
       <c r="W42" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X42" t="n">
         <v>1</v>
@@ -5060,7 +5060,7 @@
         <v>1</v>
       </c>
       <c r="W43" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X43" t="n">
         <v>1</v>
@@ -5167,7 +5167,7 @@
         <v>1</v>
       </c>
       <c r="W44" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X44" t="n">
         <v>1</v>
@@ -5274,7 +5274,7 @@
         <v>1</v>
       </c>
       <c r="W45" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X45" t="n">
         <v>1</v>
@@ -5381,7 +5381,7 @@
         <v>1</v>
       </c>
       <c r="W46" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X46" t="n">
         <v>1</v>
@@ -5488,7 +5488,7 @@
         <v>1</v>
       </c>
       <c r="W47" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X47" t="n">
         <v>1</v>
@@ -5595,7 +5595,7 @@
         <v>1</v>
       </c>
       <c r="W48" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X48" t="n">
         <v>1</v>
@@ -5702,7 +5702,7 @@
         <v>1</v>
       </c>
       <c r="W49" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X49" t="n">
         <v>1</v>
@@ -5809,7 +5809,7 @@
         <v>1</v>
       </c>
       <c r="W50" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X50" t="n">
         <v>1</v>
@@ -5916,7 +5916,7 @@
         <v>1</v>
       </c>
       <c r="W51" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X51" t="n">
         <v>1</v>
@@ -6023,7 +6023,7 @@
         <v>1</v>
       </c>
       <c r="W52" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X52" t="n">
         <v>1</v>
@@ -6130,7 +6130,7 @@
         <v>1</v>
       </c>
       <c r="W53" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X53" t="n">
         <v>1</v>
@@ -6237,7 +6237,7 @@
         <v>1</v>
       </c>
       <c r="W54" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X54" t="n">
         <v>1</v>
@@ -6344,7 +6344,7 @@
         <v>1</v>
       </c>
       <c r="W55" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X55" t="n">
         <v>1</v>
@@ -6451,7 +6451,7 @@
         <v>1</v>
       </c>
       <c r="W56" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X56" t="n">
         <v>1</v>
@@ -6558,7 +6558,7 @@
         <v>1</v>
       </c>
       <c r="W57" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X57" t="n">
         <v>1</v>
@@ -6665,7 +6665,7 @@
         <v>1</v>
       </c>
       <c r="W58" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X58" t="n">
         <v>1</v>
@@ -6772,7 +6772,7 @@
         <v>1</v>
       </c>
       <c r="W59" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X59" t="n">
         <v>1</v>
@@ -6879,7 +6879,7 @@
         <v>1</v>
       </c>
       <c r="W60" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X60" t="n">
         <v>1</v>
@@ -6986,7 +6986,7 @@
         <v>1</v>
       </c>
       <c r="W61" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X61" t="n">
         <v>1</v>
@@ -7093,7 +7093,7 @@
         <v>1</v>
       </c>
       <c r="W62" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X62" t="n">
         <v>1</v>
@@ -7200,7 +7200,7 @@
         <v>1</v>
       </c>
       <c r="W63" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X63" t="n">
         <v>1</v>
@@ -7307,7 +7307,7 @@
         <v>1</v>
       </c>
       <c r="W64" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X64" t="n">
         <v>1</v>
@@ -7414,7 +7414,7 @@
         <v>1</v>
       </c>
       <c r="W65" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X65" t="n">
         <v>1</v>
@@ -7521,7 +7521,7 @@
         <v>1</v>
       </c>
       <c r="W66" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X66" t="n">
         <v>1</v>
@@ -7628,7 +7628,7 @@
         <v>1</v>
       </c>
       <c r="W67" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X67" t="n">
         <v>1</v>
@@ -7735,7 +7735,7 @@
         <v>1</v>
       </c>
       <c r="W68" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X68" t="n">
         <v>1</v>
@@ -7842,7 +7842,7 @@
         <v>1</v>
       </c>
       <c r="W69" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X69" t="n">
         <v>1</v>
@@ -7949,7 +7949,7 @@
         <v>1</v>
       </c>
       <c r="W70" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X70" t="n">
         <v>1</v>
@@ -8056,7 +8056,7 @@
         <v>1</v>
       </c>
       <c r="W71" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X71" t="n">
         <v>1</v>
@@ -8163,7 +8163,7 @@
         <v>1</v>
       </c>
       <c r="W72" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X72" t="n">
         <v>1</v>
@@ -8270,7 +8270,7 @@
         <v>1</v>
       </c>
       <c r="W73" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X73" t="n">
         <v>1</v>
@@ -8377,7 +8377,7 @@
         <v>1</v>
       </c>
       <c r="W74" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X74" t="n">
         <v>1</v>
@@ -8484,7 +8484,7 @@
         <v>1</v>
       </c>
       <c r="W75" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X75" t="n">
         <v>1</v>
@@ -8591,7 +8591,7 @@
         <v>1</v>
       </c>
       <c r="W76" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X76" t="n">
         <v>1</v>
@@ -8698,7 +8698,7 @@
         <v>1</v>
       </c>
       <c r="W77" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X77" t="n">
         <v>1</v>
@@ -8805,7 +8805,7 @@
         <v>1</v>
       </c>
       <c r="W78" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X78" t="n">
         <v>1</v>
@@ -8912,7 +8912,7 @@
         <v>1</v>
       </c>
       <c r="W79" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X79" t="n">
         <v>1</v>
@@ -9019,7 +9019,7 @@
         <v>1</v>
       </c>
       <c r="W80" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X80" t="n">
         <v>1</v>
@@ -9126,7 +9126,7 @@
         <v>1</v>
       </c>
       <c r="W81" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X81" t="n">
         <v>1</v>
@@ -9233,7 +9233,7 @@
         <v>1</v>
       </c>
       <c r="W82" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X82" t="n">
         <v>1</v>
@@ -9340,7 +9340,7 @@
         <v>1</v>
       </c>
       <c r="W83" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X83" t="n">
         <v>1</v>
@@ -9447,7 +9447,7 @@
         <v>1</v>
       </c>
       <c r="W84" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X84" t="n">
         <v>1</v>
@@ -9554,7 +9554,7 @@
         <v>1</v>
       </c>
       <c r="W85" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X85" t="n">
         <v>1</v>
@@ -9661,7 +9661,7 @@
         <v>1</v>
       </c>
       <c r="W86" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X86" t="n">
         <v>1</v>
@@ -9768,7 +9768,7 @@
         <v>1</v>
       </c>
       <c r="W87" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X87" t="n">
         <v>1</v>
@@ -9875,7 +9875,7 @@
         <v>1</v>
       </c>
       <c r="W88" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X88" t="n">
         <v>1</v>
@@ -9982,7 +9982,7 @@
         <v>1</v>
       </c>
       <c r="W89" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X89" t="n">
         <v>1</v>
@@ -10089,7 +10089,7 @@
         <v>1</v>
       </c>
       <c r="W90" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X90" t="n">
         <v>1</v>
@@ -10196,7 +10196,7 @@
         <v>1</v>
       </c>
       <c r="W91" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X91" t="n">
         <v>1</v>
@@ -10303,7 +10303,7 @@
         <v>1</v>
       </c>
       <c r="W92" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X92" t="n">
         <v>1</v>
@@ -10410,7 +10410,7 @@
         <v>1</v>
       </c>
       <c r="W93" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X93" t="n">
         <v>1</v>
@@ -10517,7 +10517,7 @@
         <v>1</v>
       </c>
       <c r="W94" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X94" t="n">
         <v>1</v>
@@ -10624,7 +10624,7 @@
         <v>1</v>
       </c>
       <c r="W95" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X95" t="n">
         <v>1</v>
@@ -10731,7 +10731,7 @@
         <v>1</v>
       </c>
       <c r="W96" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X96" t="n">
         <v>1</v>
@@ -10838,7 +10838,7 @@
         <v>1</v>
       </c>
       <c r="W97" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X97" t="n">
         <v>1</v>
@@ -10945,7 +10945,7 @@
         <v>1</v>
       </c>
       <c r="W98" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X98" t="n">
         <v>1</v>
@@ -11052,7 +11052,7 @@
         <v>1</v>
       </c>
       <c r="W99" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X99" t="n">
         <v>1</v>
@@ -11159,7 +11159,7 @@
         <v>1</v>
       </c>
       <c r="W100" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X100" t="n">
         <v>1</v>
@@ -11266,7 +11266,7 @@
         <v>1</v>
       </c>
       <c r="W101" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X101" t="n">
         <v>1</v>
@@ -11373,7 +11373,7 @@
         <v>1</v>
       </c>
       <c r="W102" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X102" t="n">
         <v>1</v>
@@ -11480,7 +11480,7 @@
         <v>1</v>
       </c>
       <c r="W103" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X103" t="n">
         <v>1</v>
@@ -11587,7 +11587,7 @@
         <v>1</v>
       </c>
       <c r="W104" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X104" t="n">
         <v>1</v>
@@ -11694,7 +11694,7 @@
         <v>1</v>
       </c>
       <c r="W105" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X105" t="n">
         <v>1</v>
@@ -11801,7 +11801,7 @@
         <v>1</v>
       </c>
       <c r="W106" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X106" t="n">
         <v>1</v>
@@ -11908,7 +11908,7 @@
         <v>1</v>
       </c>
       <c r="W107" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X107" t="n">
         <v>4</v>
@@ -12015,7 +12015,7 @@
         <v>1</v>
       </c>
       <c r="W108" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X108" t="n">
         <v>1</v>
@@ -12122,7 +12122,7 @@
         <v>1</v>
       </c>
       <c r="W109" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X109" t="n">
         <v>1</v>
@@ -12229,7 +12229,7 @@
         <v>1</v>
       </c>
       <c r="W110" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X110" t="n">
         <v>1</v>
@@ -12336,7 +12336,7 @@
         <v>1</v>
       </c>
       <c r="W111" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X111" t="n">
         <v>1</v>
@@ -12443,7 +12443,7 @@
         <v>1</v>
       </c>
       <c r="W112" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X112" t="n">
         <v>1</v>
@@ -12550,7 +12550,7 @@
         <v>1</v>
       </c>
       <c r="W113" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X113" t="n">
         <v>1</v>
@@ -12657,7 +12657,7 @@
         <v>1</v>
       </c>
       <c r="W114" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X114" t="n">
         <v>1</v>
@@ -12764,7 +12764,7 @@
         <v>1</v>
       </c>
       <c r="W115" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X115" t="n">
         <v>1</v>
@@ -12871,7 +12871,7 @@
         <v>1</v>
       </c>
       <c r="W116" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X116" t="n">
         <v>1</v>
@@ -12978,7 +12978,7 @@
         <v>1</v>
       </c>
       <c r="W117" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X117" t="n">
         <v>1</v>
@@ -13085,7 +13085,7 @@
         <v>1</v>
       </c>
       <c r="W118" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X118" t="n">
         <v>1</v>
@@ -13192,7 +13192,7 @@
         <v>1</v>
       </c>
       <c r="W119" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X119" t="n">
         <v>1</v>
@@ -13299,7 +13299,7 @@
         <v>1</v>
       </c>
       <c r="W120" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X120" t="n">
         <v>1</v>
@@ -13406,7 +13406,7 @@
         <v>1</v>
       </c>
       <c r="W121" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X121" t="n">
         <v>1</v>
@@ -13513,7 +13513,7 @@
         <v>1</v>
       </c>
       <c r="W122" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X122" t="n">
         <v>1</v>
@@ -13620,7 +13620,7 @@
         <v>1</v>
       </c>
       <c r="W123" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X123" t="n">
         <v>1</v>
@@ -13727,7 +13727,7 @@
         <v>1</v>
       </c>
       <c r="W124" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X124" t="n">
         <v>1</v>
@@ -13834,7 +13834,7 @@
         <v>1</v>
       </c>
       <c r="W125" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X125" t="n">
         <v>1</v>
@@ -13941,7 +13941,7 @@
         <v>1</v>
       </c>
       <c r="W126" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X126" t="n">
         <v>1</v>
@@ -14048,7 +14048,7 @@
         <v>1</v>
       </c>
       <c r="W127" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X127" t="n">
         <v>1</v>
@@ -14155,7 +14155,7 @@
         <v>1</v>
       </c>
       <c r="W128" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X128" t="n">
         <v>1</v>
@@ -14262,7 +14262,7 @@
         <v>1</v>
       </c>
       <c r="W129" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X129" t="n">
         <v>1</v>
@@ -14369,7 +14369,7 @@
         <v>1</v>
       </c>
       <c r="W130" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X130" t="n">
         <v>1</v>
@@ -14476,7 +14476,7 @@
         <v>1</v>
       </c>
       <c r="W131" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X131" t="n">
         <v>1</v>
@@ -14583,7 +14583,7 @@
         <v>1</v>
       </c>
       <c r="W132" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X132" t="n">
         <v>1</v>
@@ -14690,7 +14690,7 @@
         <v>1</v>
       </c>
       <c r="W133" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X133" t="n">
         <v>1</v>
@@ -14797,7 +14797,7 @@
         <v>1</v>
       </c>
       <c r="W134" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X134" t="n">
         <v>1</v>
@@ -14904,7 +14904,7 @@
         <v>1</v>
       </c>
       <c r="W135" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X135" t="n">
         <v>1</v>
@@ -15011,7 +15011,7 @@
         <v>1</v>
       </c>
       <c r="W136" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X136" t="n">
         <v>1</v>
@@ -15118,7 +15118,7 @@
         <v>1</v>
       </c>
       <c r="W137" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X137" t="n">
         <v>1</v>
@@ -15225,7 +15225,7 @@
         <v>1</v>
       </c>
       <c r="W138" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X138" t="n">
         <v>0</v>
@@ -15332,7 +15332,7 @@
         <v>1</v>
       </c>
       <c r="W139" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X139" t="n">
         <v>0</v>
@@ -15437,7 +15437,7 @@
         <v>1</v>
       </c>
       <c r="W140" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X140" t="n">
         <v>0</v>
@@ -15544,7 +15544,7 @@
         <v>1</v>
       </c>
       <c r="W141" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X141" t="n">
         <v>0</v>
@@ -15651,7 +15651,7 @@
         <v>1</v>
       </c>
       <c r="W142" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X142" t="n">
         <v>1</v>
@@ -15758,7 +15758,7 @@
         <v>1</v>
       </c>
       <c r="W143" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X143" t="n">
         <v>1</v>
@@ -15865,7 +15865,7 @@
         <v>1</v>
       </c>
       <c r="W144" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X144" t="n">
         <v>1</v>
@@ -15972,7 +15972,7 @@
         <v>1</v>
       </c>
       <c r="W145" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X145" t="n">
         <v>1</v>
@@ -16079,7 +16079,7 @@
         <v>1</v>
       </c>
       <c r="W146" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X146" t="n">
         <v>1</v>
@@ -16184,7 +16184,7 @@
         <v>1</v>
       </c>
       <c r="W147" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X147" t="n">
         <v>1</v>
@@ -16291,7 +16291,7 @@
         <v>1</v>
       </c>
       <c r="W148" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X148" t="n">
         <v>0</v>
@@ -16398,7 +16398,7 @@
         <v>1</v>
       </c>
       <c r="W149" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X149" t="n">
         <v>0</v>
@@ -16505,7 +16505,7 @@
         <v>1</v>
       </c>
       <c r="W150" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X150" t="n">
         <v>0</v>
@@ -16612,7 +16612,7 @@
         <v>1</v>
       </c>
       <c r="W151" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X151" t="n">
         <v>1</v>
@@ -16719,7 +16719,7 @@
         <v>1</v>
       </c>
       <c r="W152" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X152" t="n">
         <v>1</v>
@@ -16826,7 +16826,7 @@
         <v>1</v>
       </c>
       <c r="W153" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X153" t="n">
         <v>1</v>
@@ -16933,7 +16933,7 @@
         <v>1</v>
       </c>
       <c r="W154" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X154" t="n">
         <v>1</v>
@@ -17040,7 +17040,7 @@
         <v>1</v>
       </c>
       <c r="W155" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X155" t="n">
         <v>0</v>
@@ -17147,7 +17147,7 @@
         <v>1</v>
       </c>
       <c r="W156" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X156" t="n">
         <v>0</v>
@@ -17254,7 +17254,7 @@
         <v>1</v>
       </c>
       <c r="W157" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X157" t="n">
         <v>0</v>
@@ -17361,7 +17361,7 @@
         <v>1</v>
       </c>
       <c r="W158" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X158" t="n">
         <v>1</v>
@@ -17468,7 +17468,7 @@
         <v>1</v>
       </c>
       <c r="W159" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X159" t="n">
         <v>1</v>
@@ -17575,7 +17575,7 @@
         <v>1</v>
       </c>
       <c r="W160" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X160" t="n">
         <v>1</v>
@@ -17682,7 +17682,7 @@
         <v>1</v>
       </c>
       <c r="W161" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X161" t="n">
         <v>0</v>
@@ -17789,7 +17789,7 @@
         <v>1</v>
       </c>
       <c r="W162" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X162" t="n">
         <v>0</v>
@@ -17896,7 +17896,7 @@
         <v>1</v>
       </c>
       <c r="W163" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X163" t="n">
         <v>1</v>
@@ -18003,7 +18003,7 @@
         <v>1</v>
       </c>
       <c r="W164" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X164" t="n">
         <v>1</v>
@@ -18110,7 +18110,7 @@
         <v>1</v>
       </c>
       <c r="W165" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X165" t="n">
         <v>1</v>
@@ -18217,7 +18217,7 @@
         <v>1</v>
       </c>
       <c r="W166" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X166" t="n">
         <v>1</v>
@@ -18324,7 +18324,7 @@
         <v>1</v>
       </c>
       <c r="W167" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X167" t="n">
         <v>1</v>
@@ -18431,7 +18431,7 @@
         <v>1</v>
       </c>
       <c r="W168" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X168" t="n">
         <v>1</v>
@@ -18538,7 +18538,7 @@
         <v>1</v>
       </c>
       <c r="W169" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X169" t="n">
         <v>1</v>
@@ -18645,7 +18645,7 @@
         <v>1</v>
       </c>
       <c r="W170" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X170" t="n">
         <v>1</v>
@@ -18752,7 +18752,7 @@
         <v>1</v>
       </c>
       <c r="W171" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X171" t="n">
         <v>1</v>
@@ -18859,7 +18859,7 @@
         <v>1</v>
       </c>
       <c r="W172" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X172" t="n">
         <v>1</v>
@@ -18966,7 +18966,7 @@
         <v>1</v>
       </c>
       <c r="W173" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X173" t="n">
         <v>1</v>
@@ -19073,7 +19073,7 @@
         <v>1</v>
       </c>
       <c r="W174" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X174" t="n">
         <v>1</v>
@@ -19180,7 +19180,7 @@
         <v>1</v>
       </c>
       <c r="W175" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X175" t="n">
         <v>1</v>
@@ -19287,7 +19287,7 @@
         <v>1</v>
       </c>
       <c r="W176" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X176" t="n">
         <v>1</v>
@@ -19394,7 +19394,7 @@
         <v>1</v>
       </c>
       <c r="W177" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X177" t="n">
         <v>1</v>
@@ -19501,7 +19501,7 @@
         <v>1</v>
       </c>
       <c r="W178" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X178" t="n">
         <v>1</v>
@@ -19608,7 +19608,7 @@
         <v>1</v>
       </c>
       <c r="W179" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X179" t="n">
         <v>1</v>
@@ -19715,7 +19715,7 @@
         <v>1</v>
       </c>
       <c r="W180" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X180" t="n">
         <v>1</v>
@@ -19822,7 +19822,7 @@
         <v>1</v>
       </c>
       <c r="W181" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X181" t="n">
         <v>1</v>
@@ -19929,7 +19929,7 @@
         <v>1</v>
       </c>
       <c r="W182" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X182" t="n">
         <v>1</v>
@@ -20036,7 +20036,7 @@
         <v>1</v>
       </c>
       <c r="W183" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X183" t="n">
         <v>1</v>
@@ -20143,7 +20143,7 @@
         <v>1</v>
       </c>
       <c r="W184" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X184" t="n">
         <v>1</v>
@@ -20250,7 +20250,7 @@
         <v>1</v>
       </c>
       <c r="W185" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X185" t="n">
         <v>1</v>
@@ -20357,7 +20357,7 @@
         <v>1</v>
       </c>
       <c r="W186" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X186" t="n">
         <v>1</v>
@@ -20464,7 +20464,7 @@
         <v>1</v>
       </c>
       <c r="W187" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X187" t="n">
         <v>1</v>
@@ -20571,7 +20571,7 @@
         <v>1</v>
       </c>
       <c r="W188" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X188" t="n">
         <v>1</v>
@@ -20678,7 +20678,7 @@
         <v>1</v>
       </c>
       <c r="W189" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X189" t="n">
         <v>1</v>
@@ -20785,7 +20785,7 @@
         <v>1</v>
       </c>
       <c r="W190" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X190" t="n">
         <v>1</v>
@@ -20892,7 +20892,7 @@
         <v>1</v>
       </c>
       <c r="W191" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X191" t="n">
         <v>1</v>
@@ -20999,7 +20999,7 @@
         <v>1</v>
       </c>
       <c r="W192" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X192" t="n">
         <v>1</v>
@@ -21106,7 +21106,7 @@
         <v>1</v>
       </c>
       <c r="W193" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X193" t="n">
         <v>1</v>
@@ -21213,7 +21213,7 @@
         <v>1</v>
       </c>
       <c r="W194" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X194" t="n">
         <v>1</v>
@@ -21320,7 +21320,7 @@
         <v>1</v>
       </c>
       <c r="W195" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X195" t="n">
         <v>1</v>
@@ -21427,7 +21427,7 @@
         <v>1</v>
       </c>
       <c r="W196" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X196" t="n">
         <v>1</v>
@@ -21534,7 +21534,7 @@
         <v>1</v>
       </c>
       <c r="W197" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X197" t="n">
         <v>1</v>
@@ -21641,7 +21641,7 @@
         <v>1</v>
       </c>
       <c r="W198" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X198" t="n">
         <v>1</v>
@@ -21748,7 +21748,7 @@
         <v>1</v>
       </c>
       <c r="W199" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X199" t="n">
         <v>1</v>
@@ -21855,7 +21855,7 @@
         <v>1</v>
       </c>
       <c r="W200" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X200" t="n">
         <v>1</v>
@@ -21962,7 +21962,7 @@
         <v>1</v>
       </c>
       <c r="W201" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X201" t="n">
         <v>1</v>
@@ -22069,7 +22069,7 @@
         <v>1</v>
       </c>
       <c r="W202" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X202" t="n">
         <v>1</v>
@@ -22176,7 +22176,7 @@
         <v>1</v>
       </c>
       <c r="W203" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X203" t="n">
         <v>1</v>
@@ -22283,7 +22283,7 @@
         <v>1</v>
       </c>
       <c r="W204" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X204" t="n">
         <v>1</v>
@@ -22390,7 +22390,7 @@
         <v>1</v>
       </c>
       <c r="W205" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X205" t="n">
         <v>1</v>
@@ -22497,7 +22497,7 @@
         <v>1</v>
       </c>
       <c r="W206" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X206" t="n">
         <v>1</v>
@@ -22604,7 +22604,7 @@
         <v>1</v>
       </c>
       <c r="W207" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X207" t="n">
         <v>4</v>
@@ -22711,7 +22711,7 @@
         <v>1</v>
       </c>
       <c r="W208" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X208" t="n">
         <v>1</v>
@@ -22818,7 +22818,7 @@
         <v>1</v>
       </c>
       <c r="W209" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X209" t="n">
         <v>1</v>
@@ -22925,7 +22925,7 @@
         <v>1</v>
       </c>
       <c r="W210" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X210" t="n">
         <v>1</v>
@@ -23032,7 +23032,7 @@
         <v>1</v>
       </c>
       <c r="W211" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X211" t="n">
         <v>1</v>
@@ -23139,7 +23139,7 @@
         <v>1</v>
       </c>
       <c r="W212" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X212" t="n">
         <v>1</v>
@@ -23246,7 +23246,7 @@
         <v>1</v>
       </c>
       <c r="W213" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X213" t="n">
         <v>1</v>
@@ -23353,7 +23353,7 @@
         <v>1</v>
       </c>
       <c r="W214" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X214" t="n">
         <v>1</v>
@@ -23460,7 +23460,7 @@
         <v>1</v>
       </c>
       <c r="W215" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X215" t="n">
         <v>1</v>
@@ -23567,7 +23567,7 @@
         <v>1</v>
       </c>
       <c r="W216" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X216" t="n">
         <v>1</v>
@@ -23674,7 +23674,7 @@
         <v>1</v>
       </c>
       <c r="W217" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X217" t="n">
         <v>0</v>
@@ -23781,7 +23781,7 @@
         <v>1</v>
       </c>
       <c r="W218" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X218" t="n">
         <v>0</v>
@@ -23888,7 +23888,7 @@
         <v>1</v>
       </c>
       <c r="W219" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X219" t="n">
         <v>0</v>
@@ -23995,7 +23995,7 @@
         <v>1</v>
       </c>
       <c r="W220" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X220" t="n">
         <v>1</v>
@@ -24102,7 +24102,7 @@
         <v>1</v>
       </c>
       <c r="W221" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X221" t="n">
         <v>1</v>
@@ -24209,7 +24209,7 @@
         <v>1</v>
       </c>
       <c r="W222" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X222" t="n">
         <v>1</v>
@@ -24316,7 +24316,7 @@
         <v>1</v>
       </c>
       <c r="W223" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X223" t="n">
         <v>1</v>
@@ -24423,7 +24423,7 @@
         <v>1</v>
       </c>
       <c r="W224" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X224" t="n">
         <v>1</v>
@@ -24530,7 +24530,7 @@
         <v>1</v>
       </c>
       <c r="W225" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X225" t="n">
         <v>1</v>
@@ -24637,7 +24637,7 @@
         <v>1</v>
       </c>
       <c r="W226" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X226" t="n">
         <v>1</v>
@@ -24744,7 +24744,7 @@
         <v>1</v>
       </c>
       <c r="W227" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X227" t="n">
         <v>1</v>
@@ -24851,7 +24851,7 @@
         <v>1</v>
       </c>
       <c r="W228" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X228" t="n">
         <v>1</v>
@@ -24958,7 +24958,7 @@
         <v>1</v>
       </c>
       <c r="W229" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X229" t="n">
         <v>1</v>
@@ -25065,7 +25065,7 @@
         <v>1</v>
       </c>
       <c r="W230" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X230" t="n">
         <v>1</v>
@@ -25172,7 +25172,7 @@
         <v>1</v>
       </c>
       <c r="W231" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X231" t="n">
         <v>1</v>
@@ -25279,7 +25279,7 @@
         <v>1</v>
       </c>
       <c r="W232" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X232" t="n">
         <v>1</v>
@@ -25386,7 +25386,7 @@
         <v>1</v>
       </c>
       <c r="W233" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X233" t="n">
         <v>1</v>
@@ -25493,7 +25493,7 @@
         <v>1</v>
       </c>
       <c r="W234" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X234" t="n">
         <v>1</v>
@@ -25600,7 +25600,7 @@
         <v>1</v>
       </c>
       <c r="W235" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X235" t="n">
         <v>1</v>
@@ -25707,7 +25707,7 @@
         <v>1</v>
       </c>
       <c r="W236" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X236" t="n">
         <v>1</v>
@@ -25814,7 +25814,7 @@
         <v>1</v>
       </c>
       <c r="W237" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X237" t="n">
         <v>1</v>
@@ -25921,7 +25921,7 @@
         <v>1</v>
       </c>
       <c r="W238" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X238" t="n">
         <v>1</v>
@@ -26028,7 +26028,7 @@
         <v>1</v>
       </c>
       <c r="W239" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X239" t="n">
         <v>1</v>
@@ -26135,7 +26135,7 @@
         <v>1</v>
       </c>
       <c r="W240" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X240" t="n">
         <v>1</v>
@@ -26242,7 +26242,7 @@
         <v>1</v>
       </c>
       <c r="W241" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X241" t="n">
         <v>1</v>
@@ -26349,7 +26349,7 @@
         <v>1</v>
       </c>
       <c r="W242" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X242" t="n">
         <v>1</v>
@@ -26456,7 +26456,7 @@
         <v>1</v>
       </c>
       <c r="W243" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X243" t="n">
         <v>1</v>
@@ -26563,7 +26563,7 @@
         <v>1</v>
       </c>
       <c r="W244" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X244" t="n">
         <v>1</v>
@@ -26670,7 +26670,7 @@
         <v>1</v>
       </c>
       <c r="W245" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X245" t="n">
         <v>1</v>
@@ -26777,7 +26777,7 @@
         <v>1</v>
       </c>
       <c r="W246" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X246" t="n">
         <v>1</v>
@@ -26884,7 +26884,7 @@
         <v>1</v>
       </c>
       <c r="W247" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X247" t="n">
         <v>1</v>
@@ -26991,7 +26991,7 @@
         <v>1</v>
       </c>
       <c r="W248" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X248" t="n">
         <v>1</v>
@@ -27098,7 +27098,7 @@
         <v>1</v>
       </c>
       <c r="W249" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X249" t="n">
         <v>1</v>
@@ -27205,7 +27205,7 @@
         <v>1</v>
       </c>
       <c r="W250" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X250" t="n">
         <v>1</v>
@@ -27312,7 +27312,7 @@
         <v>1</v>
       </c>
       <c r="W251" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X251" t="n">
         <v>1</v>
@@ -27419,7 +27419,7 @@
         <v>1</v>
       </c>
       <c r="W252" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X252" t="n">
         <v>1</v>
@@ -27526,7 +27526,7 @@
         <v>1</v>
       </c>
       <c r="W253" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X253" t="n">
         <v>1</v>
@@ -27633,7 +27633,7 @@
         <v>1</v>
       </c>
       <c r="W254" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X254" t="n">
         <v>1</v>
@@ -27740,7 +27740,7 @@
         <v>1</v>
       </c>
       <c r="W255" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X255" t="n">
         <v>1</v>
@@ -27847,7 +27847,7 @@
         <v>1</v>
       </c>
       <c r="W256" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X256" t="n">
         <v>1</v>
@@ -27954,7 +27954,7 @@
         <v>1</v>
       </c>
       <c r="W257" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X257" t="n">
         <v>1</v>
@@ -28061,7 +28061,7 @@
         <v>1</v>
       </c>
       <c r="W258" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X258" t="n">
         <v>1</v>
@@ -28168,7 +28168,7 @@
         <v>1</v>
       </c>
       <c r="W259" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X259" t="n">
         <v>1</v>
@@ -28275,7 +28275,7 @@
         <v>1</v>
       </c>
       <c r="W260" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X260" t="n">
         <v>1</v>
@@ -28382,7 +28382,7 @@
         <v>1</v>
       </c>
       <c r="W261" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X261" t="n">
         <v>1</v>
@@ -28489,7 +28489,7 @@
         <v>1</v>
       </c>
       <c r="W262" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X262" t="n">
         <v>1</v>
@@ -56400,7 +56400,7 @@
         <v>1</v>
       </c>
       <c r="W523" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X523" t="n">
         <v>1</v>
@@ -56507,7 +56507,7 @@
         <v>1</v>
       </c>
       <c r="W524" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X524" t="n">
         <v>4</v>
@@ -56614,7 +56614,7 @@
         <v>1</v>
       </c>
       <c r="W525" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X525" t="n">
         <v>4</v>
@@ -56721,7 +56721,7 @@
         <v>1</v>
       </c>
       <c r="W526" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X526" t="n">
         <v>1</v>
@@ -56828,7 +56828,7 @@
         <v>1</v>
       </c>
       <c r="W527" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X527" t="n">
         <v>4</v>
@@ -56935,7 +56935,7 @@
         <v>1</v>
       </c>
       <c r="W528" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X528" t="n">
         <v>1</v>
@@ -57042,7 +57042,7 @@
         <v>1</v>
       </c>
       <c r="W529" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X529" t="n">
         <v>1</v>
@@ -57149,7 +57149,7 @@
         <v>1</v>
       </c>
       <c r="W530" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X530" t="n">
         <v>1</v>
@@ -57256,7 +57256,7 @@
         <v>1</v>
       </c>
       <c r="W531" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X531" t="n">
         <v>1</v>
@@ -57363,7 +57363,7 @@
         <v>1</v>
       </c>
       <c r="W532" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X532" t="n">
         <v>1</v>
@@ -57470,7 +57470,7 @@
         <v>1</v>
       </c>
       <c r="W533" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X533" t="n">
         <v>1</v>
@@ -57575,7 +57575,7 @@
         <v>1</v>
       </c>
       <c r="W534" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X534" t="n">
         <v>1</v>
@@ -57680,7 +57680,7 @@
         <v>1</v>
       </c>
       <c r="W535" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X535" t="n">
         <v>4</v>
@@ -57787,7 +57787,7 @@
         <v>1</v>
       </c>
       <c r="W536" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X536" t="n">
         <v>1</v>
@@ -57894,7 +57894,7 @@
         <v>1</v>
       </c>
       <c r="W537" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X537" t="n">
         <v>1</v>
@@ -58001,7 +58001,7 @@
         <v>1</v>
       </c>
       <c r="W538" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X538" t="n">
         <v>1</v>
@@ -58108,7 +58108,7 @@
         <v>1</v>
       </c>
       <c r="W539" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X539" t="n">
         <v>1</v>
@@ -58215,7 +58215,7 @@
         <v>1</v>
       </c>
       <c r="W540" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X540" t="n">
         <v>1</v>
@@ -58322,7 +58322,7 @@
         <v>1</v>
       </c>
       <c r="W541" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X541" t="n">
         <v>1</v>
@@ -58427,7 +58427,7 @@
         <v>1</v>
       </c>
       <c r="W542" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X542" t="n">
         <v>1</v>
@@ -58532,7 +58532,7 @@
         <v>1</v>
       </c>
       <c r="W543" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X543" t="n">
         <v>4</v>
@@ -58639,7 +58639,7 @@
         <v>1</v>
       </c>
       <c r="W544" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X544" t="n">
         <v>1</v>
@@ -58746,7 +58746,7 @@
         <v>1</v>
       </c>
       <c r="W545" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X545" t="n">
         <v>1</v>
@@ -58853,7 +58853,7 @@
         <v>1</v>
       </c>
       <c r="W546" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X546" t="n">
         <v>4</v>
@@ -58960,7 +58960,7 @@
         <v>1</v>
       </c>
       <c r="W547" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X547" t="n">
         <v>1</v>
@@ -59067,7 +59067,7 @@
         <v>1</v>
       </c>
       <c r="W548" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X548" t="n">
         <v>1</v>
@@ -59174,7 +59174,7 @@
         <v>1</v>
       </c>
       <c r="W549" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X549" t="n">
         <v>1</v>
@@ -59281,7 +59281,7 @@
         <v>1</v>
       </c>
       <c r="W550" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X550" t="n">
         <v>1</v>
@@ -59388,7 +59388,7 @@
         <v>1</v>
       </c>
       <c r="W551" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X551" t="n">
         <v>4</v>
@@ -59495,7 +59495,7 @@
         <v>1</v>
       </c>
       <c r="W552" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X552" t="n">
         <v>1</v>
@@ -59602,7 +59602,7 @@
         <v>1</v>
       </c>
       <c r="W553" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X553" t="n">
         <v>1</v>
@@ -59709,7 +59709,7 @@
         <v>1</v>
       </c>
       <c r="W554" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X554" t="n">
         <v>1</v>
@@ -59816,7 +59816,7 @@
         <v>1</v>
       </c>
       <c r="W555" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X555" t="n">
         <v>4</v>
@@ -59923,7 +59923,7 @@
         <v>1</v>
       </c>
       <c r="W556" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X556" t="n">
         <v>1</v>
@@ -60030,7 +60030,7 @@
         <v>1</v>
       </c>
       <c r="W557" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X557" t="n">
         <v>1</v>
@@ -60137,7 +60137,7 @@
         <v>1</v>
       </c>
       <c r="W558" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X558" t="n">
         <v>1</v>
@@ -60244,7 +60244,7 @@
         <v>1</v>
       </c>
       <c r="W559" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X559" t="n">
         <v>1</v>
@@ -60351,7 +60351,7 @@
         <v>1</v>
       </c>
       <c r="W560" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X560" t="n">
         <v>1</v>
@@ -60458,7 +60458,7 @@
         <v>1</v>
       </c>
       <c r="W561" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X561" t="n">
         <v>1</v>
@@ -60565,7 +60565,7 @@
         <v>1</v>
       </c>
       <c r="W562" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X562" t="n">
         <v>1</v>
@@ -60672,7 +60672,7 @@
         <v>1</v>
       </c>
       <c r="W563" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X563" t="n">
         <v>7</v>
@@ -60775,7 +60775,7 @@
         <v>1</v>
       </c>
       <c r="W564" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X564" t="n">
         <v>1</v>
@@ -60882,7 +60882,7 @@
         <v>1</v>
       </c>
       <c r="W565" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X565" t="n">
         <v>1</v>
@@ -60989,7 +60989,7 @@
         <v>1</v>
       </c>
       <c r="W566" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X566" t="n">
         <v>1</v>
@@ -61096,7 +61096,7 @@
         <v>1</v>
       </c>
       <c r="W567" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X567" t="n">
         <v>1</v>
@@ -61203,7 +61203,7 @@
         <v>1</v>
       </c>
       <c r="W568" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X568" t="n">
         <v>0</v>
@@ -61310,7 +61310,7 @@
         <v>1</v>
       </c>
       <c r="W569" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X569" t="n">
         <v>1</v>
@@ -61417,7 +61417,7 @@
         <v>1</v>
       </c>
       <c r="W570" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X570" t="n">
         <v>1</v>
@@ -61524,7 +61524,7 @@
         <v>1</v>
       </c>
       <c r="W571" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X571" t="n">
         <v>1</v>
@@ -61631,7 +61631,7 @@
         <v>1</v>
       </c>
       <c r="W572" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X572" t="n">
         <v>0</v>
@@ -61738,7 +61738,7 @@
         <v>1</v>
       </c>
       <c r="W573" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X573" t="n">
         <v>1</v>
@@ -61845,7 +61845,7 @@
         <v>1</v>
       </c>
       <c r="W574" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X574" t="n">
         <v>1</v>
@@ -61952,7 +61952,7 @@
         <v>1</v>
       </c>
       <c r="W575" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X575" t="n">
         <v>1</v>
@@ -62059,7 +62059,7 @@
         <v>1</v>
       </c>
       <c r="W576" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X576" t="n">
         <v>1</v>
@@ -62166,7 +62166,7 @@
         <v>1</v>
       </c>
       <c r="W577" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X577" t="n">
         <v>1</v>
@@ -62273,7 +62273,7 @@
         <v>1</v>
       </c>
       <c r="W578" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X578" t="n">
         <v>1</v>
@@ -62380,7 +62380,7 @@
         <v>1</v>
       </c>
       <c r="W579" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X579" t="n">
         <v>8</v>
@@ -62487,7 +62487,7 @@
         <v>1</v>
       </c>
       <c r="W580" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X580" t="n">
         <v>1</v>
@@ -62594,7 +62594,7 @@
         <v>1</v>
       </c>
       <c r="W581" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X581" t="n">
         <v>1</v>
@@ -62701,7 +62701,7 @@
         <v>1</v>
       </c>
       <c r="W582" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X582" t="n">
         <v>1</v>
@@ -62808,7 +62808,7 @@
         <v>1</v>
       </c>
       <c r="W583" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X583" t="n">
         <v>1</v>
@@ -62915,7 +62915,7 @@
         <v>1</v>
       </c>
       <c r="W584" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X584" t="n">
         <v>4</v>
@@ -63022,7 +63022,7 @@
         <v>1</v>
       </c>
       <c r="W585" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X585" t="n">
         <v>1</v>
@@ -63129,7 +63129,7 @@
         <v>1</v>
       </c>
       <c r="W586" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X586" t="n">
         <v>1</v>
@@ -63236,7 +63236,7 @@
         <v>1</v>
       </c>
       <c r="W587" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X587" t="n">
         <v>1</v>
@@ -63343,7 +63343,7 @@
         <v>1</v>
       </c>
       <c r="W588" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X588" t="n">
         <v>1</v>
@@ -63450,7 +63450,7 @@
         <v>1</v>
       </c>
       <c r="W589" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X589" t="n">
         <v>1</v>
@@ -63557,7 +63557,7 @@
         <v>1</v>
       </c>
       <c r="W590" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X590" t="n">
         <v>1</v>
@@ -63664,7 +63664,7 @@
         <v>1</v>
       </c>
       <c r="W591" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X591" t="n">
         <v>0</v>
@@ -63771,7 +63771,7 @@
         <v>1</v>
       </c>
       <c r="W592" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X592" t="n">
         <v>8</v>
@@ -63878,7 +63878,7 @@
         <v>1</v>
       </c>
       <c r="W593" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X593" t="n">
         <v>8</v>
@@ -63985,7 +63985,7 @@
         <v>1</v>
       </c>
       <c r="W594" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X594" t="n">
         <v>0</v>
@@ -64092,7 +64092,7 @@
         <v>1</v>
       </c>
       <c r="W595" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X595" t="n">
         <v>1</v>
@@ -64199,7 +64199,7 @@
         <v>1</v>
       </c>
       <c r="W596" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X596" t="n">
         <v>1</v>
@@ -64306,7 +64306,7 @@
         <v>1</v>
       </c>
       <c r="W597" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X597" t="n">
         <v>8</v>
@@ -64413,7 +64413,7 @@
         <v>1</v>
       </c>
       <c r="W598" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X598" t="n">
         <v>8</v>
@@ -64520,7 +64520,7 @@
         <v>1</v>
       </c>
       <c r="W599" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X599" t="n">
         <v>1</v>
@@ -64627,7 +64627,7 @@
         <v>1</v>
       </c>
       <c r="W600" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X600" t="n">
         <v>1</v>
@@ -64734,7 +64734,7 @@
         <v>1</v>
       </c>
       <c r="W601" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X601" t="n">
         <v>1</v>
@@ -64841,7 +64841,7 @@
         <v>1</v>
       </c>
       <c r="W602" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X602" t="n">
         <v>1</v>
@@ -64948,7 +64948,7 @@
         <v>1</v>
       </c>
       <c r="W603" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X603" t="n">
         <v>1</v>
@@ -65055,7 +65055,7 @@
         <v>1</v>
       </c>
       <c r="W604" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X604" t="n">
         <v>1</v>
@@ -65162,7 +65162,7 @@
         <v>1</v>
       </c>
       <c r="W605" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X605" t="n">
         <v>1</v>
@@ -65269,7 +65269,7 @@
         <v>1</v>
       </c>
       <c r="W606" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X606" t="n">
         <v>1</v>
@@ -65376,7 +65376,7 @@
         <v>1</v>
       </c>
       <c r="W607" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X607" t="n">
         <v>1</v>
@@ -65483,7 +65483,7 @@
         <v>1</v>
       </c>
       <c r="W608" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X608" t="n">
         <v>1</v>
@@ -65590,7 +65590,7 @@
         <v>1</v>
       </c>
       <c r="W609" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X609" t="n">
         <v>1</v>
@@ -65697,7 +65697,7 @@
         <v>1</v>
       </c>
       <c r="W610" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X610" t="n">
         <v>1</v>
@@ -65804,7 +65804,7 @@
         <v>1</v>
       </c>
       <c r="W611" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X611" t="n">
         <v>1</v>
@@ -65911,7 +65911,7 @@
         <v>1</v>
       </c>
       <c r="W612" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X612" t="n">
         <v>1</v>
@@ -66018,7 +66018,7 @@
         <v>1</v>
       </c>
       <c r="W613" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X613" t="n">
         <v>1</v>
@@ -66125,7 +66125,7 @@
         <v>1</v>
       </c>
       <c r="W614" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X614" t="n">
         <v>1</v>
@@ -66232,7 +66232,7 @@
         <v>1</v>
       </c>
       <c r="W615" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X615" t="n">
         <v>1</v>
@@ -66339,7 +66339,7 @@
         <v>1</v>
       </c>
       <c r="W616" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X616" t="n">
         <v>1</v>
@@ -66446,7 +66446,7 @@
         <v>1</v>
       </c>
       <c r="W617" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X617" t="n">
         <v>1</v>
@@ -66553,7 +66553,7 @@
         <v>1</v>
       </c>
       <c r="W618" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X618" t="n">
         <v>1</v>
@@ -66660,7 +66660,7 @@
         <v>1</v>
       </c>
       <c r="W619" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X619" t="n">
         <v>1</v>
@@ -66767,7 +66767,7 @@
         <v>1</v>
       </c>
       <c r="W620" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X620" t="n">
         <v>1</v>
@@ -66874,7 +66874,7 @@
         <v>1</v>
       </c>
       <c r="W621" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X621" t="n">
         <v>1</v>
@@ -66981,7 +66981,7 @@
         <v>1</v>
       </c>
       <c r="W622" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X622" t="n">
         <v>1</v>
@@ -67088,7 +67088,7 @@
         <v>1</v>
       </c>
       <c r="W623" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X623" t="n">
         <v>1</v>
@@ -67195,7 +67195,7 @@
         <v>1</v>
       </c>
       <c r="W624" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X624" t="n">
         <v>1</v>
@@ -67302,7 +67302,7 @@
         <v>1</v>
       </c>
       <c r="W625" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X625" t="n">
         <v>1</v>
@@ -67409,7 +67409,7 @@
         <v>1</v>
       </c>
       <c r="W626" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X626" t="n">
         <v>0</v>
@@ -67516,7 +67516,7 @@
         <v>1</v>
       </c>
       <c r="W627" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X627" t="n">
         <v>0</v>
@@ -67623,7 +67623,7 @@
         <v>1</v>
       </c>
       <c r="W628" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X628" t="n">
         <v>1</v>
@@ -67730,7 +67730,7 @@
         <v>1</v>
       </c>
       <c r="W629" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X629" t="n">
         <v>1</v>
@@ -67837,7 +67837,7 @@
         <v>1</v>
       </c>
       <c r="W630" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X630" t="n">
         <v>1</v>
@@ -67944,7 +67944,7 @@
         <v>1</v>
       </c>
       <c r="W631" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X631" t="n">
         <v>1</v>
@@ -68051,7 +68051,7 @@
         <v>1</v>
       </c>
       <c r="W632" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X632" t="n">
         <v>1</v>
@@ -68158,7 +68158,7 @@
         <v>1</v>
       </c>
       <c r="W633" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X633" t="n">
         <v>1</v>
@@ -68265,7 +68265,7 @@
         <v>1</v>
       </c>
       <c r="W634" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X634" t="n">
         <v>1</v>
@@ -68372,7 +68372,7 @@
         <v>1</v>
       </c>
       <c r="W635" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X635" t="n">
         <v>1</v>
@@ -68479,7 +68479,7 @@
         <v>1</v>
       </c>
       <c r="W636" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X636" t="n">
         <v>1</v>
@@ -68586,7 +68586,7 @@
         <v>1</v>
       </c>
       <c r="W637" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X637" t="n">
         <v>1</v>
@@ -68693,7 +68693,7 @@
         <v>1</v>
       </c>
       <c r="W638" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X638" t="n">
         <v>1</v>
@@ -68800,7 +68800,7 @@
         <v>1</v>
       </c>
       <c r="W639" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X639" t="n">
         <v>1</v>
@@ -68907,7 +68907,7 @@
         <v>1</v>
       </c>
       <c r="W640" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X640" t="n">
         <v>4</v>
@@ -69014,7 +69014,7 @@
         <v>1</v>
       </c>
       <c r="W641" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X641" t="n">
         <v>1</v>
@@ -69121,7 +69121,7 @@
         <v>1</v>
       </c>
       <c r="W642" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X642" t="n">
         <v>4</v>
@@ -69228,7 +69228,7 @@
         <v>1</v>
       </c>
       <c r="W643" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X643" t="n">
         <v>4</v>
@@ -69335,7 +69335,7 @@
         <v>1</v>
       </c>
       <c r="W644" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X644" t="n">
         <v>1</v>
@@ -69442,7 +69442,7 @@
         <v>1</v>
       </c>
       <c r="W645" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X645" t="n">
         <v>1</v>
@@ -69549,7 +69549,7 @@
         <v>1</v>
       </c>
       <c r="W646" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X646" t="n">
         <v>1</v>
@@ -69656,7 +69656,7 @@
         <v>1</v>
       </c>
       <c r="W647" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X647" t="n">
         <v>4</v>
@@ -69763,7 +69763,7 @@
         <v>1</v>
       </c>
       <c r="W648" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X648" t="n">
         <v>4</v>
@@ -69870,7 +69870,7 @@
         <v>1</v>
       </c>
       <c r="W649" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X649" t="n">
         <v>4</v>
@@ -69977,7 +69977,7 @@
         <v>1</v>
       </c>
       <c r="W650" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X650" t="n">
         <v>4</v>
@@ -70084,7 +70084,7 @@
         <v>1</v>
       </c>
       <c r="W651" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X651" t="n">
         <v>4</v>
@@ -70191,7 +70191,7 @@
         <v>1</v>
       </c>
       <c r="W652" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X652" t="n">
         <v>1</v>
@@ -70298,7 +70298,7 @@
         <v>1</v>
       </c>
       <c r="W653" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X653" t="n">
         <v>1</v>
@@ -70405,7 +70405,7 @@
         <v>1</v>
       </c>
       <c r="W654" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X654" t="n">
         <v>1</v>
@@ -70512,7 +70512,7 @@
         <v>1</v>
       </c>
       <c r="W655" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X655" t="n">
         <v>1</v>
@@ -70619,7 +70619,7 @@
         <v>1</v>
       </c>
       <c r="W656" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X656" t="n">
         <v>1</v>
@@ -70726,7 +70726,7 @@
         <v>1</v>
       </c>
       <c r="W657" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X657" t="n">
         <v>1</v>
@@ -70833,7 +70833,7 @@
         <v>1</v>
       </c>
       <c r="W658" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X658" t="n">
         <v>1</v>
@@ -70940,7 +70940,7 @@
         <v>1</v>
       </c>
       <c r="W659" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X659" t="n">
         <v>1</v>
@@ -71047,7 +71047,7 @@
         <v>1</v>
       </c>
       <c r="W660" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X660" t="n">
         <v>1</v>
@@ -71152,7 +71152,7 @@
         <v>1</v>
       </c>
       <c r="W661" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X661" t="n">
         <v>1</v>
@@ -71259,7 +71259,7 @@
         <v>1</v>
       </c>
       <c r="W662" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X662" t="n">
         <v>1</v>
@@ -71366,7 +71366,7 @@
         <v>1</v>
       </c>
       <c r="W663" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X663" t="n">
         <v>1</v>
@@ -71473,7 +71473,7 @@
         <v>1</v>
       </c>
       <c r="W664" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X664" t="n">
         <v>1</v>
@@ -71580,7 +71580,7 @@
         <v>1</v>
       </c>
       <c r="W665" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X665" t="n">
         <v>1</v>
@@ -71687,7 +71687,7 @@
         <v>1</v>
       </c>
       <c r="W666" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X666" t="n">
         <v>1</v>
@@ -71794,7 +71794,7 @@
         <v>1</v>
       </c>
       <c r="W667" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X667" t="n">
         <v>1</v>
@@ -71901,7 +71901,7 @@
         <v>1</v>
       </c>
       <c r="W668" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X668" t="n">
         <v>1</v>
@@ -72008,7 +72008,7 @@
         <v>1</v>
       </c>
       <c r="W669" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X669" t="n">
         <v>1</v>
@@ -72115,7 +72115,7 @@
         <v>1</v>
       </c>
       <c r="W670" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X670" t="n">
         <v>1</v>
@@ -72222,7 +72222,7 @@
         <v>1</v>
       </c>
       <c r="W671" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X671" t="n">
         <v>1</v>
@@ -72329,7 +72329,7 @@
         <v>1</v>
       </c>
       <c r="W672" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X672" t="n">
         <v>1</v>
@@ -72436,7 +72436,7 @@
         <v>1</v>
       </c>
       <c r="W673" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X673" t="n">
         <v>1</v>
@@ -72543,7 +72543,7 @@
         <v>1</v>
       </c>
       <c r="W674" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X674" t="n">
         <v>1</v>
@@ -72650,7 +72650,7 @@
         <v>1</v>
       </c>
       <c r="W675" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X675" t="n">
         <v>1</v>
@@ -72757,7 +72757,7 @@
         <v>1</v>
       </c>
       <c r="W676" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X676" t="n">
         <v>1</v>
@@ -72864,7 +72864,7 @@
         <v>1</v>
       </c>
       <c r="W677" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X677" t="n">
         <v>1</v>
@@ -72971,7 +72971,7 @@
         <v>1</v>
       </c>
       <c r="W678" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X678" t="n">
         <v>1</v>
@@ -73078,7 +73078,7 @@
         <v>1</v>
       </c>
       <c r="W679" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X679" t="n">
         <v>0</v>
@@ -73185,7 +73185,7 @@
         <v>1</v>
       </c>
       <c r="W680" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X680" t="n">
         <v>0</v>
@@ -73292,7 +73292,7 @@
         <v>1</v>
       </c>
       <c r="W681" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X681" t="n">
         <v>1</v>
@@ -73399,7 +73399,7 @@
         <v>1</v>
       </c>
       <c r="W682" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X682" t="n">
         <v>1</v>
@@ -73506,7 +73506,7 @@
         <v>1</v>
       </c>
       <c r="W683" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X683" t="n">
         <v>1</v>
@@ -73613,7 +73613,7 @@
         <v>1</v>
       </c>
       <c r="W684" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X684" t="n">
         <v>1</v>
@@ -73720,7 +73720,7 @@
         <v>1</v>
       </c>
       <c r="W685" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X685" t="n">
         <v>1</v>
@@ -73827,7 +73827,7 @@
         <v>1</v>
       </c>
       <c r="W686" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X686" t="n">
         <v>1</v>
@@ -73934,7 +73934,7 @@
         <v>1</v>
       </c>
       <c r="W687" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X687" t="n">
         <v>1</v>
@@ -74041,7 +74041,7 @@
         <v>1</v>
       </c>
       <c r="W688" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X688" t="n">
         <v>1</v>
@@ -74148,7 +74148,7 @@
         <v>1</v>
       </c>
       <c r="W689" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X689" t="n">
         <v>1</v>
@@ -74255,7 +74255,7 @@
         <v>1</v>
       </c>
       <c r="W690" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X690" t="n">
         <v>1</v>
@@ -74362,7 +74362,7 @@
         <v>1</v>
       </c>
       <c r="W691" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X691" t="n">
         <v>1</v>
@@ -74469,7 +74469,7 @@
         <v>1</v>
       </c>
       <c r="W692" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X692" t="n">
         <v>1</v>
@@ -74576,7 +74576,7 @@
         <v>1</v>
       </c>
       <c r="W693" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X693" t="n">
         <v>1</v>
@@ -74683,7 +74683,7 @@
         <v>1</v>
       </c>
       <c r="W694" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X694" t="n">
         <v>1</v>
@@ -74790,7 +74790,7 @@
         <v>1</v>
       </c>
       <c r="W695" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X695" t="n">
         <v>1</v>
@@ -74897,7 +74897,7 @@
         <v>1</v>
       </c>
       <c r="W696" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X696" t="n">
         <v>1</v>
@@ -75004,7 +75004,7 @@
         <v>1</v>
       </c>
       <c r="W697" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X697" t="n">
         <v>1</v>
@@ -75111,7 +75111,7 @@
         <v>1</v>
       </c>
       <c r="W698" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X698" t="n">
         <v>1</v>
@@ -75218,7 +75218,7 @@
         <v>1</v>
       </c>
       <c r="W699" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X699" t="n">
         <v>1</v>
@@ -75325,7 +75325,7 @@
         <v>1</v>
       </c>
       <c r="W700" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X700" t="n">
         <v>1</v>
@@ -75432,7 +75432,7 @@
         <v>1</v>
       </c>
       <c r="W701" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X701" t="n">
         <v>1</v>
@@ -75539,7 +75539,7 @@
         <v>1</v>
       </c>
       <c r="W702" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X702" t="n">
         <v>1</v>
@@ -75646,7 +75646,7 @@
         <v>1</v>
       </c>
       <c r="W703" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X703" t="n">
         <v>1</v>
@@ -75753,7 +75753,7 @@
         <v>1</v>
       </c>
       <c r="W704" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X704" t="n">
         <v>1</v>
@@ -75860,7 +75860,7 @@
         <v>1</v>
       </c>
       <c r="W705" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X705" t="n">
         <v>4</v>
@@ -75967,7 +75967,7 @@
         <v>1</v>
       </c>
       <c r="W706" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X706" t="n">
         <v>1</v>
@@ -76074,7 +76074,7 @@
         <v>1</v>
       </c>
       <c r="W707" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X707" t="n">
         <v>1</v>
@@ -76181,7 +76181,7 @@
         <v>1</v>
       </c>
       <c r="W708" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X708" t="n">
         <v>1</v>
@@ -76288,7 +76288,7 @@
         <v>1</v>
       </c>
       <c r="W709" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X709" t="n">
         <v>1</v>
@@ -76395,7 +76395,7 @@
         <v>1</v>
       </c>
       <c r="W710" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X710" t="n">
         <v>1</v>
@@ -76502,7 +76502,7 @@
         <v>1</v>
       </c>
       <c r="W711" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X711" t="n">
         <v>4</v>
@@ -76609,7 +76609,7 @@
         <v>1</v>
       </c>
       <c r="W712" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X712" t="n">
         <v>4</v>
@@ -76716,7 +76716,7 @@
         <v>1</v>
       </c>
       <c r="W713" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X713" t="n">
         <v>1</v>
@@ -76823,7 +76823,7 @@
         <v>1</v>
       </c>
       <c r="W714" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X714" t="n">
         <v>1</v>
@@ -76930,7 +76930,7 @@
         <v>1</v>
       </c>
       <c r="W715" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X715" t="n">
         <v>4</v>
@@ -77037,7 +77037,7 @@
         <v>1</v>
       </c>
       <c r="W716" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X716" t="n">
         <v>1</v>
@@ -77142,7 +77142,7 @@
         <v>1</v>
       </c>
       <c r="W717" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X717" t="n">
         <v>1</v>
@@ -77249,7 +77249,7 @@
         <v>1</v>
       </c>
       <c r="W718" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X718" t="n">
         <v>1</v>
@@ -77356,7 +77356,7 @@
         <v>1</v>
       </c>
       <c r="W719" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X719" t="n">
         <v>4</v>
@@ -77463,7 +77463,7 @@
         <v>1</v>
       </c>
       <c r="W720" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X720" t="n">
         <v>4</v>
@@ -77570,7 +77570,7 @@
         <v>1</v>
       </c>
       <c r="W721" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X721" t="n">
         <v>1</v>
@@ -77677,7 +77677,7 @@
         <v>1</v>
       </c>
       <c r="W722" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X722" t="n">
         <v>1</v>
@@ -77784,7 +77784,7 @@
         <v>1</v>
       </c>
       <c r="W723" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X723" t="n">
         <v>1</v>
@@ -77891,7 +77891,7 @@
         <v>1</v>
       </c>
       <c r="W724" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X724" t="n">
         <v>1</v>
@@ -77998,7 +77998,7 @@
         <v>1</v>
       </c>
       <c r="W725" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X725" t="n">
         <v>1</v>
@@ -78105,7 +78105,7 @@
         <v>1</v>
       </c>
       <c r="W726" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X726" t="n">
         <v>1</v>
@@ -78212,7 +78212,7 @@
         <v>1</v>
       </c>
       <c r="W727" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X727" t="n">
         <v>1</v>
@@ -78319,7 +78319,7 @@
         <v>1</v>
       </c>
       <c r="W728" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X728" t="n">
         <v>0</v>
@@ -78426,7 +78426,7 @@
         <v>1</v>
       </c>
       <c r="W729" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X729" t="n">
         <v>1</v>
@@ -78533,7 +78533,7 @@
         <v>1</v>
       </c>
       <c r="W730" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X730" t="n">
         <v>1</v>
@@ -78640,7 +78640,7 @@
         <v>1</v>
       </c>
       <c r="W731" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X731" t="n">
         <v>4</v>
@@ -78747,7 +78747,7 @@
         <v>1</v>
       </c>
       <c r="W732" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X732" t="n">
         <v>4</v>
@@ -78854,7 +78854,7 @@
         <v>1</v>
       </c>
       <c r="W733" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X733" t="n">
         <v>8</v>
@@ -78961,7 +78961,7 @@
         <v>1</v>
       </c>
       <c r="W734" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X734" t="n">
         <v>8</v>
@@ -79068,7 +79068,7 @@
         <v>1</v>
       </c>
       <c r="W735" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X735" t="n">
         <v>4</v>
@@ -79175,7 +79175,7 @@
         <v>1</v>
       </c>
       <c r="W736" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X736" t="n">
         <v>4</v>
@@ -79282,7 +79282,7 @@
         <v>1</v>
       </c>
       <c r="W737" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X737" t="n">
         <v>4</v>
@@ -79389,7 +79389,7 @@
         <v>1</v>
       </c>
       <c r="W738" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X738" t="n">
         <v>4</v>
@@ -79496,7 +79496,7 @@
         <v>1</v>
       </c>
       <c r="W739" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X739" t="n">
         <v>1</v>
@@ -79603,7 +79603,7 @@
         <v>1</v>
       </c>
       <c r="W740" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X740" t="n">
         <v>1</v>
@@ -79710,7 +79710,7 @@
         <v>1</v>
       </c>
       <c r="W741" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X741" t="n">
         <v>1</v>
@@ -79817,7 +79817,7 @@
         <v>1</v>
       </c>
       <c r="W742" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X742" t="n">
         <v>1</v>
@@ -79922,7 +79922,7 @@
         <v>1</v>
       </c>
       <c r="W743" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X743" t="n">
         <v>1</v>
@@ -80029,7 +80029,7 @@
         <v>1</v>
       </c>
       <c r="W744" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X744" t="n">
         <v>1</v>
@@ -80136,7 +80136,7 @@
         <v>1</v>
       </c>
       <c r="W745" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X745" t="n">
         <v>1</v>
@@ -80243,7 +80243,7 @@
         <v>1</v>
       </c>
       <c r="W746" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X746" t="n">
         <v>1</v>
@@ -80350,7 +80350,7 @@
         <v>1</v>
       </c>
       <c r="W747" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X747" t="n">
         <v>1</v>
@@ -80457,7 +80457,7 @@
         <v>1</v>
       </c>
       <c r="W748" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X748" t="n">
         <v>1</v>
@@ -80564,7 +80564,7 @@
         <v>1</v>
       </c>
       <c r="W749" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X749" t="n">
         <v>1</v>
@@ -80671,7 +80671,7 @@
         <v>1</v>
       </c>
       <c r="W750" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X750" t="n">
         <v>1</v>
@@ -80778,7 +80778,7 @@
         <v>1</v>
       </c>
       <c r="W751" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X751" t="n">
         <v>1</v>
@@ -80883,7 +80883,7 @@
         <v>1</v>
       </c>
       <c r="W752" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X752" t="n">
         <v>1</v>
@@ -80990,7 +80990,7 @@
         <v>1</v>
       </c>
       <c r="W753" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X753" t="n">
         <v>1</v>
@@ -81097,7 +81097,7 @@
         <v>1</v>
       </c>
       <c r="W754" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X754" t="n">
         <v>1</v>
@@ -81204,7 +81204,7 @@
         <v>1</v>
       </c>
       <c r="W755" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X755" t="n">
         <v>1</v>
@@ -81311,7 +81311,7 @@
         <v>1</v>
       </c>
       <c r="W756" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X756" t="n">
         <v>1</v>
@@ -81418,7 +81418,7 @@
         <v>1</v>
       </c>
       <c r="W757" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X757" t="n">
         <v>1</v>
@@ -81525,7 +81525,7 @@
         <v>1</v>
       </c>
       <c r="W758" t="n">
-        <v>2810</v>
+        <v>2510</v>
       </c>
       <c r="X758" t="n">
         <v>1</v>
